--- a/results/modelling/fold/metrics_summary_all_models.xlsx
+++ b/results/modelling/fold/metrics_summary_all_models.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,32 +479,311 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>parametric_fold</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.6170804183178902</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.105366262903306</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.07226047152708</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.006018687244245</v>
+      </c>
+      <c r="F2" t="n">
+        <v>570.6301770647091</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.37145820457359</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1831.104177633461</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1881.775092850317</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>global_qP_fold</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9277773596400571</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7938864276927242</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.803605821255916</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.608372255115423</v>
+      </c>
+      <c r="F3" t="n">
+        <v>26.94161526555017</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.790190866987124</v>
+      </c>
+      <c r="H3" t="n">
+        <v>990.3961806936398</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1041.067095910496</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>global_rP_fold</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9278514038949838</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7855704396786916</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.796630613463203</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.607034831655151</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20.36770769358338</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.785286008255747</v>
+      </c>
+      <c r="H4" t="n">
+        <v>989.8792036465658</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1040.550118863422</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>global_P_fold</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.9278452922655742</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.7871840765505587</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6.797206348678928</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.60714524886492</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23.34934670224594</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4.785690856395577</v>
-      </c>
-      <c r="H2" t="n">
-        <v>989.9218951323775</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1040.592810349234</v>
+      <c r="B5" t="n">
+        <v>0.92796306777117</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7874850581396673</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.786111515930099</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.605016605691814</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23.12457196682151</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.777889140819718</v>
+      </c>
+      <c r="H5" t="n">
+        <v>989.0985621286612</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1039.769477345518</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>global_ind_qP_fold</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9280036936246041</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7842505703334315</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.782284429416219</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.604281941229908</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23.10529543616823</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.775197992503972</v>
+      </c>
+      <c r="H6" t="n">
+        <v>988.8142467737856</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1039.485161990642</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>global_ind_rP_fold</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9279629954946482</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7875622377634911</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.786118324611721</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.605017912531835</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24.2591099813054</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.77789392857981</v>
+      </c>
+      <c r="H7" t="n">
+        <v>989.0990678046744</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1039.769983021531</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9279532716030739</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7858158431132962</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.787034346581978</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.605193725345963</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22.34570947039661</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.778538061126462</v>
+      </c>
+      <c r="H8" t="n">
+        <v>989.1670954891622</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1039.838010706019</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>induction_qP_fold</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9278155305051585</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.7987948464973751</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.800010002566493</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.607682879984929</v>
+      </c>
+      <c r="F9" t="n">
+        <v>31.03954251413968</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.787662342644998</v>
+      </c>
+      <c r="H9" t="n">
+        <v>990.1297379059065</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1040.800653122763</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>induction_rP_fold</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9279509079477642</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7881912094162903</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.787257010540875</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.605236459621444</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24.49283296184193</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.778694634994283</v>
+      </c>
+      <c r="H10" t="n">
+        <v>989.1836300738919</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1039.854545290748</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9278060386059956</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7926221705112618</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.800904170102839</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.607854323021675</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22.71078141588476</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.788291107490189</v>
+      </c>
+      <c r="H11" t="n">
+        <v>990.1960070453549</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1040.866922262211</v>
       </c>
     </row>
   </sheetData>
@@ -518,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,7 +855,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>parametric_fold</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -585,34 +864,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8005465547938748</v>
+        <v>-135.6591363296641</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1492902187498827</v>
+        <v>4.648006464514677</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09287839281289882</v>
+        <v>63.63731111478562</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3047595655806374</v>
+        <v>7.977299738306542</v>
       </c>
       <c r="G2" t="n">
-        <v>30.13402441666043</v>
+        <v>1045.380126509084</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1308509085308667</v>
+        <v>171.0997173584983</v>
       </c>
       <c r="I2" t="n">
-        <v>-16.39989217607675</v>
+        <v>94.60439916837404</v>
       </c>
       <c r="J2" t="n">
-        <v>-6.401332047402157</v>
+        <v>104.6029592970486</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>parametric_fold</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -621,34 +900,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9584156672460971</v>
+        <v>-67.00241232875298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07213629115672146</v>
+        <v>3.022412975155626</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01651818546309257</v>
+        <v>27.0120111204287</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1285230931120651</v>
+        <v>5.197308064799382</v>
       </c>
       <c r="G3" t="n">
-        <v>33.47809911998309</v>
+        <v>1101.547105775528</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03003802965033568</v>
+        <v>78.63026296585198</v>
       </c>
       <c r="I3" t="n">
-        <v>-37.54940033576815</v>
+        <v>73.44422435095905</v>
       </c>
       <c r="J3" t="n">
-        <v>-29.05279792254163</v>
+        <v>81.94082676418556</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>parametric_fold</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -657,34 +936,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9717913157995759</v>
+        <v>-3264.481482321026</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008742817522964443</v>
+        <v>3.457856389600832</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000370310578062508</v>
+        <v>42.86773274424948</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01924345546055874</v>
+        <v>6.547345473109654</v>
       </c>
       <c r="G4" t="n">
-        <v>16.28639062043155</v>
+        <v>6033.091559173914</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01472182266477099</v>
+        <v>2019.315715234565</v>
       </c>
       <c r="I4" t="n">
-        <v>-141.9245385893836</v>
+        <v>102.9205072413069</v>
       </c>
       <c r="J4" t="n">
-        <v>-129.3902693367026</v>
+        <v>115.4547764939879</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>parametric_fold</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -693,34 +972,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09440684190958415</v>
+        <v>-2881.917784130143</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03441064619329541</v>
+        <v>2.090270522989905</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006089598856466664</v>
+        <v>19.38598219817107</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07803588185230345</v>
+        <v>4.402951532571199</v>
       </c>
       <c r="G5" t="n">
-        <v>68.21298670007528</v>
+        <v>4089.976162178394</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2819406666266515</v>
+        <v>1756.903045555525</v>
       </c>
       <c r="I5" t="n">
-        <v>-83.12463444158909</v>
+        <v>86.25555499353264</v>
       </c>
       <c r="J5" t="n">
-        <v>-70.59036518890801</v>
+        <v>98.78982424621373</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>parametric_fold</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -729,64 +1008,2008 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-5.435308422855499</v>
+        <v>-8495.226043522336</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1773619993845482</v>
+        <v>10.59477225766001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2743182405653318</v>
+        <v>362.1690875649164</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5237539885913346</v>
+        <v>19.03074059423113</v>
       </c>
       <c r="G6" t="n">
-        <v>101.5010899848057</v>
+        <v>5541.195198481908</v>
       </c>
       <c r="H6" t="n">
-        <v>4.257230590504764</v>
+        <v>5604.784348704286</v>
       </c>
       <c r="I6" t="n">
-        <v>-10.92359238560066</v>
+        <v>183.0870022783026</v>
       </c>
       <c r="J6" t="n">
-        <v>4.626450006451293</v>
+        <v>198.6370446703545</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>parametric_fold</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-2321.117397437931</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.967356041367196</v>
+      </c>
+      <c r="E7" t="n">
+        <v>87.69614757039496</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9.364622126407181</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3240.0904659053</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1516.057045061312</v>
+      </c>
+      <c r="I7" t="n">
+        <v>135.8469492762947</v>
+      </c>
+      <c r="J7" t="n">
+        <v>150.473459174713</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>global_qP_fold</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9630772019152555</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.06509990365741283</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.01719363704508692</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1311245097038953</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15.62320531271801</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0291123853569842</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-45.07467034838648</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-35.07611021971188</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>global_qP_fold</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9487728620228442</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.08184537387341309</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02034851372649893</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1426482166958246</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33.60477440432852</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.035612101001696</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-34.42121107970456</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-25.92460866647804</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>global_qP_fold</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9424698474164468</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01187166779185906</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0007552292729385641</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.02748143505966463</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21.36427804783617</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.02378770626612296</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-126.9582728230118</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-114.4240035703307</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>global_qP_fold</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9196270853381062</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0115908398825647</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0005404621322979283</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.02324784145459376</v>
+      </c>
+      <c r="G11" t="n">
+        <v>28.46460186661474</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.03049019789117669</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-133.9848056606974</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-121.4505364080163</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>global_qP_fold</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9061296946423545</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.03736342820082018</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.004001414588861886</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.06325673552169671</v>
+      </c>
+      <c r="G12" t="n">
+        <v>22.46918156639583</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.03696208181949698</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-125.0698979954607</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-109.5198556034088</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>global_qP_fold</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-12.95641901270655</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4513592221648141</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5270724824864476</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7259975774659634</v>
+      </c>
+      <c r="G13" t="n">
+        <v>252.1368717965042</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.123752883104956</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.989569950667502</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22.61607984908591</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>global_rP_fold</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.1777047864395453</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3390788365383284</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5484153340120098</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.740550696449615</v>
+      </c>
+      <c r="G14" t="n">
+        <v>49.69088836812535</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.486404339480541</v>
+      </c>
+      <c r="I14" t="n">
+        <v>13.78771970454464</v>
+      </c>
+      <c r="J14" t="n">
+        <v>23.78627983321924</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>global_rP_fold</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9552954912563036</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.068529706348437</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01775758603209795</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1332575927746631</v>
+      </c>
+      <c r="G15" t="n">
+        <v>29.464440294031</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.03184166284557748</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-36.46413708408599</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-27.96753467085947</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>global_rP_fold</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9093386606548112</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.01558918233222656</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.001190160191177343</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0344986983983069</v>
+      </c>
+      <c r="G16" t="n">
+        <v>31.1388778437074</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.03403151393738079</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-117.407014696157</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-104.8727454434759</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>global_rP_fold</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8821904008128684</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.01072045382338032</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0007922025404912841</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.02814609281039349</v>
+      </c>
+      <c r="G17" t="n">
+        <v>21.45741191892446</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.04189742153448339</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-125.9545627839085</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-113.4202935312274</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>global_rP_fold</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9245262121369766</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.03414449576652289</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.003217225241583508</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.05672058922105366</v>
+      </c>
+      <c r="G18" t="n">
+        <v>22.81498882087924</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.03089419402801547</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-130.959372462823</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-115.4093300707711</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>global_rP_fold</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.2838398408411552</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1064774886778977</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.02704621526496716</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1644573356982508</v>
+      </c>
+      <c r="G19" t="n">
+        <v>69.9979188627333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2397803984331305</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-66.2552049936557</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-51.62869509523729</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>global_P_fold</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6073303751521468</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2283008841795378</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1828523123509953</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4276123388666367</v>
+      </c>
+      <c r="G20" t="n">
+        <v>54.40532814377115</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2517975061000526</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-4.884300301154614</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5.114259827519984</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>global_P_fold</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9063456772150384</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0897593192099128</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.03720149803382704</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1928768986525526</v>
+      </c>
+      <c r="G21" t="n">
+        <v>26.18325774759989</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.06013734545916739</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-25.3710937318096</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-16.87449131858308</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>global_P_fold</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.9641675638716671</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.01172495433638124</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0004703916723585195</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.02168851475685966</v>
+      </c>
+      <c r="G22" t="n">
+        <v>21.98109466612958</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.01707900500915083</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-136.9008421619768</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-124.3665729092957</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>global_P_fold</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7112695284327581</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.02647791321291858</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.001941548181735942</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.04406300241399742</v>
+      </c>
+      <c r="G23" t="n">
+        <v>64.14814689420729</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.09397822519738773</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-107.1296614391891</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-94.59539218650798</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>global_P_fold</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.3463106845898629</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.08940744106400159</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.02786484984042101</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1669276784731071</v>
+      </c>
+      <c r="G24" t="n">
+        <v>53.15665304553558</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2216121895113358</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-72.67050966357553</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-57.12046727152358</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>global_P_fold</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>BR08</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>-0.3931082103874284</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.09707699824374214</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.05261156190227901</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.229372103583411</v>
-      </c>
-      <c r="G7" t="n">
-        <v>66.6167655885034</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.9215211128956478</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-49.620484384115</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-34.9939744856966</v>
+      <c r="C25" t="n">
+        <v>0.3402080224833306</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.1379931415225295</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.02491743728801341</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1578525808721967</v>
+      </c>
+      <c r="G25" t="n">
+        <v>94.49535701683655</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2213797993566102</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-68.3046856977671</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-53.67817579934869</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>global_ind_qP_fold</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9780564260164135</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.05774284112529374</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.01021834384490175</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1010858241540413</v>
+      </c>
+      <c r="G26" t="n">
+        <v>25.44662337302389</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.01973591288650717</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-53.92070288156583</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-43.92214275289123</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>global_ind_qP_fold</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8787405667390928</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1041759787138351</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.04816683772724877</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.2194694459993208</v>
+      </c>
+      <c r="G27" t="n">
+        <v>34.0744663676067</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0760946163873463</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-21.49626763009944</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-12.99966521687292</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>global_ind_qP_fold</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9661959885713899</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.009557906050170466</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0004437634497241814</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0210656936682413</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20.53124814605681</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.01645183784338996</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-138.1245970763238</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-125.5903278236428</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>global_ind_qP_fold</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8178704799640353</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01690279290407196</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.001224717420876427</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.03499596292254904</v>
+      </c>
+      <c r="G29" t="n">
+        <v>44.81397905833461</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.06149615820540292</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-116.8059479070512</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-104.2716786543701</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>global_ind_qP_fold</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1078163443296823</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.1278921310394761</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0380311609953932</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.1950157967842431</v>
+      </c>
+      <c r="G30" t="n">
+        <v>77.84642723292136</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3002769093978706</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-64.27243458567243</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-48.72239219362048</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>global_ind_qP_fold</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.2768276260051417</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.1484152973118481</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.04822015632613895</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.2195908839777712</v>
+      </c>
+      <c r="G31" t="n">
+        <v>93.1646750171742</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.8456047944596796</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-51.79945410746693</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-37.17294420904852</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>global_ind_rP_fold</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.9161902435951993</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.1147608396925854</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.03902722998278598</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.1975531067404053</v>
+      </c>
+      <c r="G32" t="n">
+        <v>30.08564958282436</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0584619879093904</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-31.13942642055183</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-21.14086629187723</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>global_ind_rP_fold</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.9539927281267575</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.07823929313914843</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.01827507138206552</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1351853223618064</v>
+      </c>
+      <c r="G33" t="n">
+        <v>38.32790191567435</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.03259473152941861</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-36.03326051037819</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-27.53665809715167</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>global_ind_rP_fold</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7273649973957255</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.03152525656360605</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.003579026398294193</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.05982496467440823</v>
+      </c>
+      <c r="G34" t="n">
+        <v>57.65126423200319</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.09029581926008831</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-94.28595389813901</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-81.75168464545794</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>global_ind_rP_fold</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.382583624960088</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.03305064459265225</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.004151773915049229</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.06443426041361248</v>
+      </c>
+      <c r="G35" t="n">
+        <v>74.0626186806625</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1941311542525081</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-91.16861131987156</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-78.63434206719049</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>global_ind_rP_fold</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7345870223037212</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.06051781992272023</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.01131377337040551</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.1063662228830446</v>
+      </c>
+      <c r="G36" t="n">
+        <v>39.65922104204125</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.09354353466816752</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-97.00682915534908</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-81.45678676329713</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>global_ind_rP_fold</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-2.90882034921595</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.2327157711733073</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.1476189302699401</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.3842120902183325</v>
+      </c>
+      <c r="G37" t="n">
+        <v>124.3048586192098</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.563958711907486</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-23.82802802945514</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-9.201518131036735</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7143759036629604</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.1541016707379723</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.1330050077049567</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.3646985161814573</v>
+      </c>
+      <c r="G38" t="n">
+        <v>29.38175095621351</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1847907342945815</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-10.29526449238794</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-0.2967043637133386</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.9357590505026809</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.07464108127115485</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.02551787771615221</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.1597431617195309</v>
+      </c>
+      <c r="G39" t="n">
+        <v>25.34967087143018</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.04313479925050227</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-31.0256397833467</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-22.52903737012019</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.9489093458003982</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01020567355451904</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0006706945122226501</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.02589777041026216</v>
+      </c>
+      <c r="G40" t="n">
+        <v>16.0075324138305</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.02179668241843639</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-129.4511327381758</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-116.9168634854947</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.1061125155919211</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.04125598283481639</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.007437977473543939</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.08624370976218462</v>
+      </c>
+      <c r="G41" t="n">
+        <v>84.34546561333883</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6860806778181142</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-78.92428255299635</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-66.39001330031527</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.05529769846160315</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.0912661401784936</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.04026987615630736</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.2006735561958958</v>
+      </c>
+      <c r="G42" t="n">
+        <v>50.47121902571124</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3175996037709343</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-62.72809264534753</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-47.17805025329558</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>global_ind_P_fold</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.754119254784154</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.1507233968251267</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.06624535916803671</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.25738173821784</v>
+      </c>
+      <c r="G43" t="n">
+        <v>86.24485387074829</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.157215055705744</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-43.85974667158068</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-29.23323677316228</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>induction_qP_fold</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.8778983423636537</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.1393768234973786</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.05685840978748052</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.23845001528094</v>
+      </c>
+      <c r="G44" t="n">
+        <v>37.87231511094296</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.08243138414214027</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-24.74224938521708</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-14.74368925654248</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>induction_qP_fold</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.2629263684022431</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.2819077586754642</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.2927813948281808</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.5410927783921911</v>
+      </c>
+      <c r="G45" t="n">
+        <v>94.77844361637655</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.4320690658590536</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5.575064382489661</v>
+      </c>
+      <c r="J45" t="n">
+        <v>14.07166679571618</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>induction_qP_fold</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-18.04521754098174</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.267173812152838</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.2500168198848894</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.5000168196019904</v>
+      </c>
+      <c r="G46" t="n">
+        <v>497.5127061528236</v>
+      </c>
+      <c r="H46" t="n">
+        <v>11.78915407242789</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-5.110768760713494</v>
+      </c>
+      <c r="J46" t="n">
+        <v>7.423500491967584</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>induction_qP_fold</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.83759960128235</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.01687754774293925</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.001092050302595145</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.03304618438784038</v>
+      </c>
+      <c r="G47" t="n">
+        <v>38.92781868835177</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.05548455482711161</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-119.2136650995288</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-106.6793958468477</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>induction_qP_fold</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.01891164643173726</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.1173893948322188</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.04182090636621957</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.204501604801086</v>
+      </c>
+      <c r="G48" t="n">
+        <v>71.88956558000797</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.3296011405268326</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-61.7076906289679</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-46.15764823691595</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>induction_qP_fold</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.6435676691013013</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.07444452862284283</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0134608794214452</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.1160210300826759</v>
+      </c>
+      <c r="G49" t="n">
+        <v>60.33765746917629</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.1223523148646213</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-83.69919052456692</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-69.07268062614851</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>induction_rP_fold</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.9186743790788644</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.1132248170747432</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.03787045622531155</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1946033304579126</v>
+      </c>
+      <c r="G50" t="n">
+        <v>29.44985263816072</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.05690700563405877</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-31.65092782996324</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-21.65236770128865</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>induction_rP_fold</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.955277502122106</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.07937287997870515</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.01776473170055809</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1332844015650672</v>
+      </c>
+      <c r="G51" t="n">
+        <v>37.93689786404471</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.03185206155375885</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-36.45810228482799</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-27.96149987160147</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>induction_rP_fold</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7750807780357274</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.0283251512038041</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.00295263566748381</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.0543381603248013</v>
+      </c>
+      <c r="G52" t="n">
+        <v>53.48070562757869</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.07554261155652046</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-98.32619827914304</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-85.79192902646196</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>induction_rP_fold</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.4468046350834405</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.03122422893728921</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.003719924153029212</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.06099118094470062</v>
+      </c>
+      <c r="G53" t="n">
+        <v>70.7755309332148</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1745625563820883</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-93.47509199738721</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-80.94082274470614</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>induction_rP_fold</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.7908835757779235</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.05618966172770314</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.008914017137419438</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.09441407277212141</v>
+      </c>
+      <c r="G54" t="n">
+        <v>37.58690526144422</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.07497473926281659</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-103.4435176121391</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-87.89347522008715</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>induction_rP_fold</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-3.637774300383827</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.2546568715998175</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.1751483107156371</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.4185072409357299</v>
+      </c>
+      <c r="G55" t="n">
+        <v>135.7491627177002</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3.039872215232188</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-19.55305435429238</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-4.926544455873973</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.07857686751760085</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.3333337353130066</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.4290740606518431</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.6550374498086678</v>
+      </c>
+      <c r="G56" t="n">
+        <v>55.21890071551628</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.5827787822010099</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9.615862430168713</v>
+      </c>
+      <c r="J56" t="n">
+        <v>19.61442255884331</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.462120720638594</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.1677181877507518</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.2136571421219302</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.4622306157341054</v>
+      </c>
+      <c r="G57" t="n">
+        <v>29.14891464495499</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.316923783293773</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.8492596743663299</v>
+      </c>
+      <c r="J57" t="n">
+        <v>9.345862087592849</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.8963766886448536</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.01849844643236161</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.001360318973264927</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.0368825022641486</v>
+      </c>
+      <c r="G58" t="n">
+        <v>34.90224278706977</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.03803921668782936</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-114.6007574189448</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-102.0664881662637</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.6900480364085393</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.02354891371535377</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.002084250644104035</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.04565359398890776</v>
+      </c>
+      <c r="G59" t="n">
+        <v>55.93598465298017</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1004445645283111</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-105.6402637244324</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-93.1059944717513</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.1707396630055101</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.08416859522791051</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.03534892528336719</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.1880130987015724</v>
+      </c>
+      <c r="G60" t="n">
+        <v>48.67700964922973</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.279522348796704</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-66.2471568102776</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-50.69711441822565</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>induction_P_fold</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.08254506559110553</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.1257882467589217</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.04088295963349029</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.2021953501777187</v>
+      </c>
+      <c r="G61" t="n">
+        <v>84.64490028401899</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.7187631828415498</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-55.92604844069487</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-41.29953854227647</v>
       </c>
     </row>
   </sheetData>

--- a/results/modelling/fold/metrics_summary_all_models.xlsx
+++ b/results/modelling/fold/metrics_summary_all_models.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,311 +479,280 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_fold</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6170804183178902</v>
+        <v>0.9279316425771152</v>
       </c>
       <c r="C2" t="n">
-        <v>2.105366262903306</v>
+        <v>0.7848056217733065</v>
       </c>
       <c r="D2" t="n">
-        <v>36.07226047152708</v>
+        <v>6.789071870635205</v>
       </c>
       <c r="E2" t="n">
-        <v>6.006018687244245</v>
+        <v>2.605584746392871</v>
       </c>
       <c r="F2" t="n">
-        <v>570.6301770647091</v>
+        <v>21.06671542536503</v>
       </c>
       <c r="G2" t="n">
-        <v>25.37145820457359</v>
+        <v>4.779970816671509</v>
       </c>
       <c r="H2" t="n">
-        <v>1831.104177633461</v>
+        <v>989.3183777661429</v>
       </c>
       <c r="I2" t="n">
-        <v>1881.775092850317</v>
+        <v>1039.989292982999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>global_qP_fold</t>
+          <t>global_rP_fold</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9277773596400571</v>
+        <v>0.9276813863936408</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7938864276927242</v>
+        <v>0.7952760566725968</v>
       </c>
       <c r="D3" t="n">
-        <v>6.803605821255916</v>
+        <v>6.812646810823018</v>
       </c>
       <c r="E3" t="n">
-        <v>2.608372255115423</v>
+        <v>2.610104750929169</v>
       </c>
       <c r="F3" t="n">
-        <v>26.94161526555017</v>
+        <v>21.9697105446086</v>
       </c>
       <c r="G3" t="n">
-        <v>4.790190866987124</v>
+        <v>4.79654835165802</v>
       </c>
       <c r="H3" t="n">
-        <v>990.3961806936398</v>
+        <v>991.0654778247354</v>
       </c>
       <c r="I3" t="n">
-        <v>1041.067095910496</v>
+        <v>1041.736393041592</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>global_rP_fold</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9278514038949838</v>
+        <v>0.9268513686762052</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7855704396786916</v>
+        <v>0.8568308561595733</v>
       </c>
       <c r="D4" t="n">
-        <v>6.796630613463203</v>
+        <v>6.890837158696571</v>
       </c>
       <c r="E4" t="n">
-        <v>2.607034831655151</v>
+        <v>2.625040410869244</v>
       </c>
       <c r="F4" t="n">
-        <v>20.36770769358338</v>
+        <v>44.84243941022778</v>
       </c>
       <c r="G4" t="n">
-        <v>4.785286008255747</v>
+        <v>4.851530600484738</v>
       </c>
       <c r="H4" t="n">
-        <v>989.8792036465658</v>
+        <v>996.8170608662817</v>
       </c>
       <c r="I4" t="n">
-        <v>1040.550118863422</v>
+        <v>1047.487976083138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_fold</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.92796306777117</v>
+        <v>0.9277523099795385</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7874850581396673</v>
+        <v>0.8037467043952824</v>
       </c>
       <c r="D5" t="n">
-        <v>6.786111515930099</v>
+        <v>6.805965580124828</v>
       </c>
       <c r="E5" t="n">
-        <v>2.605016605691814</v>
+        <v>2.608824559092625</v>
       </c>
       <c r="F5" t="n">
-        <v>23.12457196682151</v>
+        <v>27.64522681816416</v>
       </c>
       <c r="G5" t="n">
-        <v>4.777889140819718</v>
+        <v>4.791850213093518</v>
       </c>
       <c r="H5" t="n">
-        <v>989.0985621286612</v>
+        <v>990.5709574660707</v>
       </c>
       <c r="I5" t="n">
-        <v>1039.769477345518</v>
+        <v>1041.241872682927</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>global_ind_qP_fold</t>
+          <t>global_ind_rP_fold</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9280036936246041</v>
+        <v>0.9271803064970326</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7842505703334315</v>
+        <v>0.8193638095597381</v>
       </c>
       <c r="D6" t="n">
-        <v>6.782284429416219</v>
+        <v>6.85985015432427</v>
       </c>
       <c r="E6" t="n">
-        <v>2.604281941229908</v>
+        <v>2.619131564913124</v>
       </c>
       <c r="F6" t="n">
-        <v>23.10529543616823</v>
+        <v>29.64960777348112</v>
       </c>
       <c r="G6" t="n">
-        <v>4.775197992503972</v>
+        <v>4.829741016077879</v>
       </c>
       <c r="H6" t="n">
-        <v>988.8142467737856</v>
+        <v>994.545541445555</v>
       </c>
       <c r="I6" t="n">
-        <v>1039.485161990642</v>
+        <v>1045.216456662411</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>global_ind_rP_fold</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9279629954946482</v>
+        <v>0.9275823472565139</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7875622377634911</v>
+        <v>0.8010407473809297</v>
       </c>
       <c r="D7" t="n">
-        <v>6.786118324611721</v>
+        <v>6.82197661719026</v>
       </c>
       <c r="E7" t="n">
-        <v>2.605017912531835</v>
+        <v>2.611891386943619</v>
       </c>
       <c r="F7" t="n">
-        <v>24.2591099813054</v>
+        <v>27.90013119018987</v>
       </c>
       <c r="G7" t="n">
-        <v>4.77789392857981</v>
+        <v>4.803108927856228</v>
       </c>
       <c r="H7" t="n">
-        <v>989.0990678046744</v>
+        <v>991.7552252413507</v>
       </c>
       <c r="I7" t="n">
-        <v>1039.769983021531</v>
+        <v>1042.426140458207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_fold</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9279532716030739</v>
+        <v>0.9278155305051585</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7858158431132962</v>
+        <v>0.7987948464973751</v>
       </c>
       <c r="D8" t="n">
-        <v>6.787034346581978</v>
+        <v>6.800010002566493</v>
       </c>
       <c r="E8" t="n">
-        <v>2.605193725345963</v>
+        <v>2.607682879984929</v>
       </c>
       <c r="F8" t="n">
-        <v>22.34570947039661</v>
+        <v>31.03954251413968</v>
       </c>
       <c r="G8" t="n">
-        <v>4.778538061126462</v>
+        <v>4.787662342644998</v>
       </c>
       <c r="H8" t="n">
-        <v>989.1670954891622</v>
+        <v>990.1297379059065</v>
       </c>
       <c r="I8" t="n">
-        <v>1039.838010706019</v>
+        <v>1040.800653122763</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>induction_qP_fold</t>
+          <t>induction_rP_fold</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9278155305051585</v>
+        <v>0.9220700575936051</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7987948464973751</v>
+        <v>0.8815889151114358</v>
       </c>
       <c r="D9" t="n">
-        <v>6.800010002566493</v>
+        <v>7.341252094410502</v>
       </c>
       <c r="E9" t="n">
-        <v>2.607682879984929</v>
+        <v>2.70947450521508</v>
       </c>
       <c r="F9" t="n">
-        <v>31.03954251413968</v>
+        <v>86.53613267357983</v>
       </c>
       <c r="G9" t="n">
-        <v>4.787662342644998</v>
+        <v>5.168255448809269</v>
       </c>
       <c r="H9" t="n">
-        <v>990.1297379059065</v>
+        <v>1028.72874422659</v>
       </c>
       <c r="I9" t="n">
-        <v>1040.800653122763</v>
+        <v>1079.399659443447</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>induction_rP_fold</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9279509079477642</v>
+        <v>0.9278427548704825</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7881912094162903</v>
+        <v>0.7950067186902156</v>
       </c>
       <c r="D10" t="n">
-        <v>6.787257010540875</v>
+        <v>6.797445379486039</v>
       </c>
       <c r="E10" t="n">
-        <v>2.605236459621444</v>
+        <v>2.607191089944509</v>
       </c>
       <c r="F10" t="n">
-        <v>24.49283296184193</v>
+        <v>26.84659779362877</v>
       </c>
       <c r="G10" t="n">
-        <v>4.778694634994283</v>
+        <v>4.785858939179082</v>
       </c>
       <c r="H10" t="n">
-        <v>989.1836300738919</v>
+        <v>989.9396185031861</v>
       </c>
       <c r="I10" t="n">
-        <v>1039.854545290748</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.9278060386059956</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7926221705112618</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6.800904170102839</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.607854323021675</v>
-      </c>
-      <c r="F11" t="n">
-        <v>22.71078141588476</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.788291107490189</v>
-      </c>
-      <c r="H11" t="n">
-        <v>990.1960070453549</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1040.866922262211</v>
+        <v>1040.610533720042</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,7 +824,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_fold</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -864,34 +833,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-135.6591363296641</v>
+        <v>0.8710421895731332</v>
       </c>
       <c r="D2" t="n">
-        <v>4.648006464514677</v>
+        <v>0.1309886903311658</v>
       </c>
       <c r="E2" t="n">
-        <v>63.63731111478562</v>
+        <v>0.06005107688533452</v>
       </c>
       <c r="F2" t="n">
-        <v>7.977299738306542</v>
+        <v>0.2450532123546527</v>
       </c>
       <c r="G2" t="n">
-        <v>1045.380126509084</v>
+        <v>32.16854190096201</v>
       </c>
       <c r="H2" t="n">
-        <v>171.0997173584983</v>
+        <v>0.08672309694779422</v>
       </c>
       <c r="I2" t="n">
-        <v>94.60439916837404</v>
+        <v>-23.81351655702944</v>
       </c>
       <c r="J2" t="n">
-        <v>104.6029592970486</v>
+        <v>-13.81495642835484</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_fold</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -900,34 +869,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-67.00241232875298</v>
+        <v>0.1632655791054169</v>
       </c>
       <c r="D3" t="n">
-        <v>3.022412975155626</v>
+        <v>0.2837500927857678</v>
       </c>
       <c r="E3" t="n">
-        <v>27.0120111204287</v>
+        <v>0.332368789695029</v>
       </c>
       <c r="F3" t="n">
-        <v>5.197308064799382</v>
+        <v>0.5765143447435016</v>
       </c>
       <c r="G3" t="n">
-        <v>1101.547105775528</v>
+        <v>81.61539894864661</v>
       </c>
       <c r="H3" t="n">
-        <v>78.63026296585198</v>
+        <v>0.4896784790548953</v>
       </c>
       <c r="I3" t="n">
-        <v>73.44422435095905</v>
+        <v>7.477348286598801</v>
       </c>
       <c r="J3" t="n">
-        <v>81.94082676418556</v>
+        <v>15.97395069982532</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_fold</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -936,34 +905,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-3264.481482321026</v>
+        <v>0.7584971306147099</v>
       </c>
       <c r="D4" t="n">
-        <v>3.457856389600832</v>
+        <v>0.02851910112242522</v>
       </c>
       <c r="E4" t="n">
-        <v>42.86773274424948</v>
+        <v>0.00317033813170472</v>
       </c>
       <c r="F4" t="n">
-        <v>6.547345473109654</v>
+        <v>0.05630575575999953</v>
       </c>
       <c r="G4" t="n">
-        <v>6033.091559173914</v>
+        <v>55.23215125303287</v>
       </c>
       <c r="H4" t="n">
-        <v>2019.315715234565</v>
+        <v>0.08067009750778034</v>
       </c>
       <c r="I4" t="n">
-        <v>102.9205072413069</v>
+        <v>-96.83225764319785</v>
       </c>
       <c r="J4" t="n">
-        <v>115.4547764939879</v>
+        <v>-84.29798839051676</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_fold</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -972,34 +941,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-2881.917784130143</v>
+        <v>0.9063169519764828</v>
       </c>
       <c r="D5" t="n">
-        <v>2.090270522989905</v>
+        <v>0.01156666810193518</v>
       </c>
       <c r="E5" t="n">
-        <v>19.38598219817107</v>
+        <v>0.0006299652079056051</v>
       </c>
       <c r="F5" t="n">
-        <v>4.402951532571199</v>
+        <v>0.02509910771134315</v>
       </c>
       <c r="G5" t="n">
-        <v>4089.976162178394</v>
+        <v>27.07520093083901</v>
       </c>
       <c r="H5" t="n">
-        <v>1756.903045555525</v>
+        <v>0.0345458900525891</v>
       </c>
       <c r="I5" t="n">
-        <v>86.25555499353264</v>
+        <v>-130.7667652786571</v>
       </c>
       <c r="J5" t="n">
-        <v>98.78982424621373</v>
+        <v>-118.2324960259761</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_fold</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1008,34 +977,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-8495.226043522336</v>
+        <v>0.8579860217921739</v>
       </c>
       <c r="D6" t="n">
-        <v>10.59477225766001</v>
+        <v>0.04702626607006518</v>
       </c>
       <c r="E6" t="n">
-        <v>362.1690875649164</v>
+        <v>0.00605363753806971</v>
       </c>
       <c r="F6" t="n">
-        <v>19.03074059423113</v>
+        <v>0.07780512539717233</v>
       </c>
       <c r="G6" t="n">
-        <v>5541.195198481908</v>
+        <v>31.32977713995114</v>
       </c>
       <c r="H6" t="n">
-        <v>5604.784348704286</v>
+        <v>0.05284173973899664</v>
       </c>
       <c r="I6" t="n">
-        <v>183.0870022783026</v>
+        <v>-113.8915904246415</v>
       </c>
       <c r="J6" t="n">
-        <v>198.6370446703545</v>
+        <v>-98.34154803258954</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>parametric_fold</t>
+          <t>global_qP_fold</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1044,34 +1013,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-2321.117397437931</v>
+        <v>0.6453772597768062</v>
       </c>
       <c r="D7" t="n">
-        <v>5.967356041367196</v>
+        <v>0.07794356396902133</v>
       </c>
       <c r="E7" t="n">
-        <v>87.69614757039496</v>
+        <v>0.01339253915101091</v>
       </c>
       <c r="F7" t="n">
-        <v>9.364622126407181</v>
+        <v>0.1157261385816139</v>
       </c>
       <c r="G7" t="n">
-        <v>3240.0904659053</v>
+        <v>54.34578175484027</v>
       </c>
       <c r="H7" t="n">
-        <v>1516.057045061312</v>
+        <v>0.1217615994726658</v>
       </c>
       <c r="I7" t="n">
-        <v>135.8469492762947</v>
+        <v>-83.82643767149986</v>
       </c>
       <c r="J7" t="n">
-        <v>150.473459174713</v>
+        <v>-69.19992777308146</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>global_qP_fold</t>
+          <t>global_rP_fold</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1080,34 +1049,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9630772019152555</v>
+        <v>-0.04945242488097978</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06509990365741283</v>
+        <v>0.3688497664478155</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01719363704508692</v>
+        <v>0.4886927596352772</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1311245097038953</v>
+        <v>0.6990656332815089</v>
       </c>
       <c r="G8" t="n">
-        <v>15.62320531271801</v>
+        <v>65.64411147138544</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0291123853569842</v>
+        <v>1.325841318417976</v>
       </c>
       <c r="I8" t="n">
-        <v>-45.07467034838648</v>
+        <v>11.82763806359259</v>
       </c>
       <c r="J8" t="n">
-        <v>-35.07611021971188</v>
+        <v>21.82619819226719</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>global_qP_fold</t>
+          <t>global_rP_fold</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1116,34 +1085,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9487728620228442</v>
+        <v>-0.624642848037221</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08184537387341309</v>
+        <v>0.3866939666437861</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02034851372649893</v>
+        <v>0.6453428514527981</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1426482166958246</v>
+        <v>0.8033323418441449</v>
       </c>
       <c r="G9" t="n">
-        <v>33.60477440432852</v>
+        <v>103.6856136892228</v>
       </c>
       <c r="H9" t="n">
-        <v>0.035612101001696</v>
+        <v>1.89026570085625</v>
       </c>
       <c r="I9" t="n">
-        <v>-34.42121107970456</v>
+        <v>17.43039673844357</v>
       </c>
       <c r="J9" t="n">
-        <v>-25.92460866647804</v>
+        <v>25.92699915167008</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>global_qP_fold</t>
+          <t>global_rP_fold</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1152,34 +1121,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9424698474164468</v>
+        <v>0.7064354785907949</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01187166779185906</v>
+        <v>0.03200402676410736</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0007552292729385641</v>
+        <v>0.003853779454911679</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02748143505966463</v>
+        <v>0.06207881647479822</v>
       </c>
       <c r="G10" t="n">
-        <v>21.36427804783617</v>
+        <v>59.98479255119392</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02378770626612296</v>
+        <v>0.09676700204119972</v>
       </c>
       <c r="I10" t="n">
-        <v>-126.9582728230118</v>
+        <v>-92.73271964783878</v>
       </c>
       <c r="J10" t="n">
-        <v>-114.4240035703307</v>
+        <v>-80.19845039515769</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>global_qP_fold</t>
+          <t>global_rP_fold</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1188,34 +1157,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9196270853381062</v>
+        <v>0.5345597047711035</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0115908398825647</v>
+        <v>0.02140002717193622</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0005404621322979283</v>
+        <v>0.003129821227399787</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02324784145459376</v>
+        <v>0.05594480518689637</v>
       </c>
       <c r="G11" t="n">
-        <v>28.46460186661474</v>
+        <v>37.74463652376375</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03049019789117669</v>
+        <v>0.1478229634278488</v>
       </c>
       <c r="I11" t="n">
-        <v>-133.9848056606974</v>
+        <v>-97.10236723006717</v>
       </c>
       <c r="J11" t="n">
-        <v>-121.4505364080163</v>
+        <v>-84.56809797738609</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>global_qP_fold</t>
+          <t>global_rP_fold</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1224,34 +1193,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9061296946423545</v>
+        <v>0.9156978624626041</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03736342820082018</v>
+        <v>0.03606480280814451</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004001414588861886</v>
+        <v>0.003593551781142707</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06325673552169671</v>
+        <v>0.059946240759056</v>
       </c>
       <c r="G12" t="n">
-        <v>22.46918156639583</v>
+        <v>25.85587063959951</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03696208181949698</v>
+        <v>0.03380612750801867</v>
       </c>
       <c r="I12" t="n">
-        <v>-125.0698979954607</v>
+        <v>-127.9725837102675</v>
       </c>
       <c r="J12" t="n">
-        <v>-109.5198556034088</v>
+        <v>-112.4225413182155</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>global_qP_fold</t>
+          <t>global_rP_fold</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1260,34 +1229,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-12.95641901270655</v>
+        <v>0.7514808778414162</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4513592221648141</v>
+        <v>0.06616669630572058</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5270724824864476</v>
+        <v>0.009385472773654945</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7259975774659634</v>
+        <v>0.09687864973075824</v>
       </c>
       <c r="G13" t="n">
-        <v>252.1368717965042</v>
+        <v>46.61305204815999</v>
       </c>
       <c r="H13" t="n">
-        <v>9.123752883104956</v>
+        <v>0.08712556758913363</v>
       </c>
       <c r="I13" t="n">
-        <v>7.989569950667502</v>
+        <v>-92.71480586891062</v>
       </c>
       <c r="J13" t="n">
-        <v>22.61607984908591</v>
+        <v>-78.08829597049221</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>global_rP_fold</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1296,34 +1265,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.1777047864395453</v>
+        <v>0.03747519473844529</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3390788365383284</v>
+        <v>0.3538077184276334</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5484153340120098</v>
+        <v>0.448213651375405</v>
       </c>
       <c r="F14" t="n">
-        <v>0.740550696449615</v>
+        <v>0.6694876036009965</v>
       </c>
       <c r="G14" t="n">
-        <v>49.69088836812535</v>
+        <v>90.10380100466767</v>
       </c>
       <c r="H14" t="n">
-        <v>1.486404339480541</v>
+        <v>0.6085069975412499</v>
       </c>
       <c r="I14" t="n">
-        <v>13.78771970454464</v>
+        <v>10.35775058243996</v>
       </c>
       <c r="J14" t="n">
-        <v>23.78627983321924</v>
+        <v>20.35631071111456</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>global_rP_fold</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,34 +1301,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9552954912563036</v>
+        <v>-0.01669120136519964</v>
       </c>
       <c r="D15" t="n">
-        <v>0.068529706348437</v>
+        <v>0.3159362214509615</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01775758603209795</v>
+        <v>0.4038514678648665</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1332575927746631</v>
+        <v>0.6354930903360527</v>
       </c>
       <c r="G15" t="n">
-        <v>29.464440294031</v>
+        <v>108.9769296159912</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03184166284557748</v>
+        <v>1.187406775829933</v>
       </c>
       <c r="I15" t="n">
-        <v>-36.46413708408599</v>
+        <v>10.39937816366924</v>
       </c>
       <c r="J15" t="n">
-        <v>-27.96753467085947</v>
+        <v>18.89598057689576</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>global_rP_fold</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1368,34 +1337,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9093386606548112</v>
+        <v>-51.81991836155307</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01558918233222656</v>
+        <v>0.501974081930127</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001190160191177343</v>
+        <v>0.6933954934837798</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0344986983983069</v>
+        <v>0.8327037249128767</v>
       </c>
       <c r="G16" t="n">
-        <v>31.1388778437074</v>
+        <v>355.1265392128344</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03403151393738079</v>
+        <v>32.67470470780914</v>
       </c>
       <c r="I16" t="n">
-        <v>-117.407014696157</v>
+        <v>16.31075035688109</v>
       </c>
       <c r="J16" t="n">
-        <v>-104.8727454434759</v>
+        <v>28.84501960956216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>global_rP_fold</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1404,34 +1373,34 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.8821904008128684</v>
+        <v>-105.3629086811794</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01072045382338032</v>
+        <v>0.516647414593433</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0007922025404912841</v>
+        <v>0.7152300580993459</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02814609281039349</v>
+        <v>0.8457127515293511</v>
       </c>
       <c r="G17" t="n">
-        <v>21.45741191892446</v>
+        <v>497.9877166624406</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04189742153448339</v>
+        <v>64.83106729004673</v>
       </c>
       <c r="I17" t="n">
-        <v>-125.9545627839085</v>
+        <v>16.96182840229513</v>
       </c>
       <c r="J17" t="n">
-        <v>-113.4202935312274</v>
+        <v>29.4960976549762</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>global_rP_fold</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1440,34 +1409,34 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9245262121369766</v>
+        <v>-8.646945490880022</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03414449576652289</v>
+        <v>0.3276264082678364</v>
       </c>
       <c r="E18" t="n">
-        <v>0.003217225241583508</v>
+        <v>0.4112208677503646</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05672058922105366</v>
+        <v>0.6412650526501227</v>
       </c>
       <c r="G18" t="n">
-        <v>22.81498882087924</v>
+        <v>179.3012400629269</v>
       </c>
       <c r="H18" t="n">
-        <v>0.03089419402801547</v>
+        <v>6.375876509378524</v>
       </c>
       <c r="I18" t="n">
-        <v>-130.959372462823</v>
+        <v>0.00712992186532091</v>
       </c>
       <c r="J18" t="n">
-        <v>-115.4093300707711</v>
+        <v>15.55717231391727</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>global_rP_fold</t>
+          <t>global_P_fold</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1476,34 +1445,34 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.2838398408411552</v>
+        <v>-2.720496552229416</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1064774886778977</v>
+        <v>0.2341255080519791</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02704621526496716</v>
+        <v>0.1405067698297444</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1644573356982508</v>
+        <v>0.3748423266251351</v>
       </c>
       <c r="G19" t="n">
-        <v>69.9979188627333</v>
+        <v>131.0639621346041</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2397803984331305</v>
+        <v>2.441007409099292</v>
       </c>
       <c r="I19" t="n">
-        <v>-66.2552049936557</v>
+        <v>-25.06249018818858</v>
       </c>
       <c r="J19" t="n">
-        <v>-51.62869509523729</v>
+        <v>-10.43598028977018</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_fold</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1512,34 +1481,34 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6073303751521468</v>
+        <v>0.1372229118395981</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2283008841795378</v>
+        <v>0.3208148832271094</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1828523123509953</v>
+        <v>0.401764678576081</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4276123388666367</v>
+        <v>0.6338490976376641</v>
       </c>
       <c r="G20" t="n">
-        <v>54.40532814377115</v>
+        <v>57.58848650663798</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2517975061000526</v>
+        <v>0.5460684014513772</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.884300301154614</v>
+        <v>8.497891446531046</v>
       </c>
       <c r="J20" t="n">
-        <v>5.114259827519984</v>
+        <v>18.49645157520564</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_fold</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1548,34 +1517,34 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9063456772150384</v>
+        <v>0.3906804027387886</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0897593192099128</v>
+        <v>0.2413965494971372</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03720149803382704</v>
+        <v>0.2420347627896689</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1928768986525526</v>
+        <v>0.4919702864906262</v>
       </c>
       <c r="G21" t="n">
-        <v>26.18325774759989</v>
+        <v>70.36864850766341</v>
       </c>
       <c r="H21" t="n">
-        <v>0.06013734545916739</v>
+        <v>0.3582202131311317</v>
       </c>
       <c r="I21" t="n">
-        <v>-25.3710937318096</v>
+        <v>2.719891271240591</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.87449131858308</v>
+        <v>11.21649368446711</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_fold</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1584,34 +1553,34 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9641675638716671</v>
+        <v>-4.285996626560502</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01172495433638124</v>
+        <v>0.0974843439628421</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0004703916723585195</v>
+        <v>0.06939212238721348</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02168851475685966</v>
+        <v>0.263423845517473</v>
       </c>
       <c r="G22" t="n">
-        <v>21.98109466612958</v>
+        <v>115.6699910516594</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01707900500915083</v>
+        <v>3.280746947278401</v>
       </c>
       <c r="I22" t="n">
-        <v>-136.9008421619768</v>
+        <v>-32.02762049183997</v>
       </c>
       <c r="J22" t="n">
-        <v>-124.3665729092957</v>
+        <v>-19.49335123915889</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_fold</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1620,34 +1589,34 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7112695284327581</v>
+        <v>-3.669613677178582</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02647791321291858</v>
+        <v>0.06434289298472363</v>
       </c>
       <c r="E23" t="n">
-        <v>0.001941548181735942</v>
+        <v>0.03140049574651124</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04406300241399742</v>
+        <v>0.1772018502908794</v>
       </c>
       <c r="G23" t="n">
-        <v>64.14814689420729</v>
+        <v>114.0683194924277</v>
       </c>
       <c r="H23" t="n">
-        <v>0.09397822519738773</v>
+        <v>2.857728900352265</v>
       </c>
       <c r="I23" t="n">
-        <v>-107.1296614391891</v>
+        <v>-48.67956355982923</v>
       </c>
       <c r="J23" t="n">
-        <v>-94.59539218650798</v>
+        <v>-36.14529430714816</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_fold</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1656,34 +1625,34 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.3463106845898629</v>
+        <v>-0.07667824519032806</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08940744106400159</v>
+        <v>0.1401898035718969</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02786484984042101</v>
+        <v>0.04589562185187774</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1669276784731071</v>
+        <v>0.2142326348899199</v>
       </c>
       <c r="G24" t="n">
-        <v>53.15665304553558</v>
+        <v>83.83605191770035</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2216121895113358</v>
+        <v>0.7222608177068257</v>
       </c>
       <c r="I24" t="n">
-        <v>-72.67050966357553</v>
+        <v>-59.19740987580414</v>
       </c>
       <c r="J24" t="n">
-        <v>-57.12046727152358</v>
+        <v>-43.64736748375219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>global_P_fold</t>
+          <t>global_ind_qP_fold</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1692,34 +1661,34 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.3402080224833306</v>
+        <v>-0.3584324999632751</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1379931415225295</v>
+        <v>0.153246651217269</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02491743728801341</v>
+        <v>0.0513020130302797</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1578525808721967</v>
+        <v>0.2264994768874306</v>
       </c>
       <c r="G25" t="n">
-        <v>94.49535701683655</v>
+        <v>95.75271578352842</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2213797993566102</v>
+        <v>0.8988823182203567</v>
       </c>
       <c r="I25" t="n">
-        <v>-68.3046856977671</v>
+        <v>-50.25063218047416</v>
       </c>
       <c r="J25" t="n">
-        <v>-53.67817579934869</v>
+        <v>-35.62412228205575</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>global_ind_qP_fold</t>
+          <t>global_ind_rP_fold</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1728,34 +1697,34 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9780564260164135</v>
+        <v>-3.17082284259061</v>
       </c>
       <c r="D26" t="n">
-        <v>0.05774284112529374</v>
+        <v>0.7656141195396576</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01021834384490175</v>
+        <v>1.942204216762488</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1010858241540413</v>
+        <v>1.393629870791556</v>
       </c>
       <c r="G26" t="n">
-        <v>25.44662337302389</v>
+        <v>142.9573396144652</v>
       </c>
       <c r="H26" t="n">
-        <v>0.01973591288650717</v>
+        <v>5.233579609021848</v>
       </c>
       <c r="I26" t="n">
-        <v>-53.92070288156583</v>
+        <v>35.28499987914366</v>
       </c>
       <c r="J26" t="n">
-        <v>-43.92214275289123</v>
+        <v>45.28356000781826</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>global_ind_qP_fold</t>
+          <t>global_ind_rP_fold</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1764,34 +1733,34 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.8787405667390928</v>
+        <v>0.2161123819303364</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1041759787138351</v>
+        <v>0.2871590612999024</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04816683772724877</v>
+        <v>0.3113769104851462</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2194694459993208</v>
+        <v>0.5580115684151594</v>
       </c>
       <c r="G27" t="n">
-        <v>34.0744663676067</v>
+        <v>92.00169440486764</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0760946163873463</v>
+        <v>0.4591301227605014</v>
       </c>
       <c r="I27" t="n">
-        <v>-21.49626763009944</v>
+        <v>6.498732453332384</v>
       </c>
       <c r="J27" t="n">
-        <v>-12.99966521687292</v>
+        <v>14.9953348665589</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>global_ind_qP_fold</t>
+          <t>global_ind_rP_fold</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1800,34 +1769,34 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9661959885713899</v>
+        <v>-5.814963583189545</v>
       </c>
       <c r="D28" t="n">
-        <v>0.009557906050170466</v>
+        <v>0.1087248962950374</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0004437634497241814</v>
+        <v>0.08946369444371023</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0210656936682413</v>
+        <v>0.2991048218329324</v>
       </c>
       <c r="G28" t="n">
-        <v>20.53124814605681</v>
+        <v>130.3668967775081</v>
       </c>
       <c r="H28" t="n">
-        <v>0.01645183784338996</v>
+        <v>4.226227322134921</v>
       </c>
       <c r="I28" t="n">
-        <v>-138.1245970763238</v>
+        <v>-26.69237007812535</v>
       </c>
       <c r="J28" t="n">
-        <v>-125.5903278236428</v>
+        <v>-14.15810082544427</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>global_ind_qP_fold</t>
+          <t>global_ind_rP_fold</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1836,34 +1805,34 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.8178704799640353</v>
+        <v>0.07680537126577258</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01690279290407196</v>
+        <v>0.03991761736248719</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001224717420876427</v>
+        <v>0.006207958734240813</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03499596292254904</v>
+        <v>0.07879060054499402</v>
       </c>
       <c r="G29" t="n">
-        <v>44.81397905833461</v>
+        <v>87.83498545754523</v>
       </c>
       <c r="H29" t="n">
-        <v>0.06149615820540292</v>
+        <v>0.2873039597342368</v>
       </c>
       <c r="I29" t="n">
-        <v>-116.8059479070512</v>
+        <v>-82.72038600959196</v>
       </c>
       <c r="J29" t="n">
-        <v>-104.2716786543701</v>
+        <v>-70.18611675691088</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>global_ind_qP_fold</t>
+          <t>global_ind_rP_fold</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1872,34 +1841,34 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1078163443296823</v>
+        <v>0.1056620710743225</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1278921310394761</v>
+        <v>0.1274798224682842</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0380311609953932</v>
+        <v>0.03812299131808736</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1950157967842431</v>
+        <v>0.1952510981226158</v>
       </c>
       <c r="G30" t="n">
-        <v>77.84642723292136</v>
+        <v>76.24223403399675</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3002769093978706</v>
+        <v>0.3009874726003645</v>
       </c>
       <c r="I30" t="n">
-        <v>-64.27243458567243</v>
+        <v>-64.20731876889371</v>
       </c>
       <c r="J30" t="n">
-        <v>-48.72239219362048</v>
+        <v>-48.65727637684176</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>global_ind_qP_fold</t>
+          <t>global_ind_rP_fold</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1908,34 +1877,34 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.2768276260051417</v>
+        <v>-0.6207052900293737</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1484152973118481</v>
+        <v>0.1629684505296156</v>
       </c>
       <c r="E31" t="n">
-        <v>0.04822015632613895</v>
+        <v>0.06120690127008738</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2195908839777712</v>
+        <v>0.2474002855093085</v>
       </c>
       <c r="G31" t="n">
-        <v>93.1646750171742</v>
+        <v>99.3748081824796</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8456047944596796</v>
+        <v>1.070112835795747</v>
       </c>
       <c r="I31" t="n">
-        <v>-51.79945410746693</v>
+        <v>-45.83738324925865</v>
       </c>
       <c r="J31" t="n">
-        <v>-37.17294420904852</v>
+        <v>-31.21087335084025</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>global_ind_rP_fold</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1944,34 +1913,34 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9161902435951993</v>
+        <v>0.28905427992869</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1147608396925854</v>
+        <v>0.3438732986019148</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03902722998278598</v>
+        <v>0.3310621974425766</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1975531067404053</v>
+        <v>0.575380046093516</v>
       </c>
       <c r="G32" t="n">
-        <v>30.08564958282436</v>
+        <v>131.8988938081492</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0584619879093904</v>
+        <v>0.4510272542311967</v>
       </c>
       <c r="I32" t="n">
-        <v>-31.13942642055183</v>
+        <v>5.207366769207816</v>
       </c>
       <c r="J32" t="n">
-        <v>-21.14086629187723</v>
+        <v>15.20592689788241</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>global_ind_rP_fold</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1980,34 +1949,34 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9539927281267575</v>
+        <v>-0.310968506839814</v>
       </c>
       <c r="D33" t="n">
-        <v>0.07823929313914843</v>
+        <v>0.3575417747760513</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01827507138206552</v>
+        <v>0.520744701145196</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1351853223618064</v>
+        <v>0.7216264276931631</v>
       </c>
       <c r="G33" t="n">
-        <v>38.32790191567435</v>
+        <v>154.0376441141564</v>
       </c>
       <c r="H33" t="n">
-        <v>0.03259473152941861</v>
+        <v>1.527623685707163</v>
       </c>
       <c r="I33" t="n">
-        <v>-36.03326051037819</v>
+        <v>14.21256938516823</v>
       </c>
       <c r="J33" t="n">
-        <v>-27.53665809715167</v>
+        <v>22.70917179839475</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>global_ind_rP_fold</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2016,34 +1985,34 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.7273649973957255</v>
+        <v>-32.89908337648875</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03152525656360605</v>
+        <v>0.22071248025575</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003579026398294193</v>
+        <v>0.4450115103471561</v>
       </c>
       <c r="F34" t="n">
-        <v>0.05982496467440823</v>
+        <v>0.6670918305204735</v>
       </c>
       <c r="G34" t="n">
-        <v>57.65126423200319</v>
+        <v>243.2365366145559</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09029581926008831</v>
+        <v>20.97446614037927</v>
       </c>
       <c r="I34" t="n">
-        <v>-94.28595389813901</v>
+        <v>6.997242244763264</v>
       </c>
       <c r="J34" t="n">
-        <v>-81.75168464545794</v>
+        <v>19.53151149744434</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>global_ind_rP_fold</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2052,34 +2021,34 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.382583624960088</v>
+        <v>0.0905084597817456</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03305064459265225</v>
+        <v>0.04122559867976912</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004151773915049229</v>
+        <v>0.006115813258746176</v>
       </c>
       <c r="F35" t="n">
-        <v>0.06443426041361248</v>
+        <v>0.07820366525135619</v>
       </c>
       <c r="G35" t="n">
-        <v>74.0626186806625</v>
+        <v>101.6616171077164</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1941311542525081</v>
+        <v>0.2831285313465987</v>
       </c>
       <c r="I35" t="n">
-        <v>-91.16861131987156</v>
+        <v>-83.0344280169066</v>
       </c>
       <c r="J35" t="n">
-        <v>-78.63434206719049</v>
+        <v>-70.50015876422552</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>global_ind_rP_fold</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2088,34 +2057,34 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.7345870223037212</v>
+        <v>0.9630114372706771</v>
       </c>
       <c r="D36" t="n">
-        <v>0.06051781992272023</v>
+        <v>0.02331838321916886</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01131377337040551</v>
+        <v>0.001576713466119466</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1063662228830446</v>
+        <v>0.03970785144174217</v>
       </c>
       <c r="G36" t="n">
-        <v>39.65922104204125</v>
+        <v>17.69597515393271</v>
       </c>
       <c r="H36" t="n">
-        <v>0.09354353466816752</v>
+        <v>0.01820026824508051</v>
       </c>
       <c r="I36" t="n">
-        <v>-97.00682915534908</v>
+        <v>-150.2151424425854</v>
       </c>
       <c r="J36" t="n">
-        <v>-81.45678676329713</v>
+        <v>-134.6651000505335</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>global_ind_rP_fold</t>
+          <t>global_ind_P_fold</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2124,34 +2093,34 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-2.90882034921595</v>
+        <v>0.7744110833231334</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2327157711733073</v>
+        <v>0.05545572638747715</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1476189302699401</v>
+        <v>0.008519499896502896</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3842120902183325</v>
+        <v>0.09230113702714011</v>
       </c>
       <c r="G37" t="n">
-        <v>124.3048586192098</v>
+        <v>35.81103891781405</v>
       </c>
       <c r="H37" t="n">
-        <v>2.563958711907486</v>
+        <v>0.07964032493061203</v>
       </c>
       <c r="I37" t="n">
-        <v>-23.82802802945514</v>
+        <v>-95.13494093643102</v>
       </c>
       <c r="J37" t="n">
-        <v>-9.201518131036735</v>
+        <v>-80.50843103801262</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_fold</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2160,34 +2129,34 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.7143759036629604</v>
+        <v>0.8778983423636537</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1541016707379723</v>
+        <v>0.1393768234973786</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1330050077049567</v>
+        <v>0.05685840978748052</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3646985161814573</v>
+        <v>0.23845001528094</v>
       </c>
       <c r="G38" t="n">
-        <v>29.38175095621351</v>
+        <v>37.87231511094296</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1847907342945815</v>
+        <v>0.08243138414214027</v>
       </c>
       <c r="I38" t="n">
-        <v>-10.29526449238794</v>
+        <v>-24.74224938521708</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2967043637133386</v>
+        <v>-14.74368925654248</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_fold</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2196,34 +2165,34 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9357590505026809</v>
+        <v>0.2629263684022431</v>
       </c>
       <c r="D39" t="n">
-        <v>0.07464108127115485</v>
+        <v>0.2819077586754642</v>
       </c>
       <c r="E39" t="n">
-        <v>0.02551787771615221</v>
+        <v>0.2927813948281808</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1597431617195309</v>
+        <v>0.5410927783921911</v>
       </c>
       <c r="G39" t="n">
-        <v>25.34967087143018</v>
+        <v>94.77844361637655</v>
       </c>
       <c r="H39" t="n">
-        <v>0.04313479925050227</v>
+        <v>0.4320690658590536</v>
       </c>
       <c r="I39" t="n">
-        <v>-31.0256397833467</v>
+        <v>5.575064382489661</v>
       </c>
       <c r="J39" t="n">
-        <v>-22.52903737012019</v>
+        <v>14.07166679571618</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_fold</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2232,34 +2201,34 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9489093458003982</v>
+        <v>-18.04521754098174</v>
       </c>
       <c r="D40" t="n">
-        <v>0.01020567355451904</v>
+        <v>0.267173812152838</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0006706945122226501</v>
+        <v>0.2500168198848894</v>
       </c>
       <c r="F40" t="n">
-        <v>0.02589777041026216</v>
+        <v>0.5000168196019904</v>
       </c>
       <c r="G40" t="n">
-        <v>16.0075324138305</v>
+        <v>497.5127061528236</v>
       </c>
       <c r="H40" t="n">
-        <v>0.02179668241843639</v>
+        <v>11.78915407242789</v>
       </c>
       <c r="I40" t="n">
-        <v>-129.4511327381758</v>
+        <v>-5.110768760713494</v>
       </c>
       <c r="J40" t="n">
-        <v>-116.9168634854947</v>
+        <v>7.423500491967584</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_fold</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2268,34 +2237,34 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.1061125155919211</v>
+        <v>0.83759960128235</v>
       </c>
       <c r="D41" t="n">
-        <v>0.04125598283481639</v>
+        <v>0.01687754774293925</v>
       </c>
       <c r="E41" t="n">
-        <v>0.007437977473543939</v>
+        <v>0.001092050302595145</v>
       </c>
       <c r="F41" t="n">
-        <v>0.08624370976218462</v>
+        <v>0.03304618438784038</v>
       </c>
       <c r="G41" t="n">
-        <v>84.34546561333883</v>
+        <v>38.92781868835177</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6860806778181142</v>
+        <v>0.05548455482711161</v>
       </c>
       <c r="I41" t="n">
-        <v>-78.92428255299635</v>
+        <v>-119.2136650995288</v>
       </c>
       <c r="J41" t="n">
-        <v>-66.39001330031527</v>
+        <v>-106.6793958468477</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_fold</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2304,34 +2273,34 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.05529769846160315</v>
+        <v>0.01891164643173726</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0912661401784936</v>
+        <v>0.1173893948322188</v>
       </c>
       <c r="E42" t="n">
-        <v>0.04026987615630736</v>
+        <v>0.04182090636621957</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2006735561958958</v>
+        <v>0.204501604801086</v>
       </c>
       <c r="G42" t="n">
-        <v>50.47121902571124</v>
+        <v>71.88956558000797</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3175996037709343</v>
+        <v>0.3296011405268326</v>
       </c>
       <c r="I42" t="n">
-        <v>-62.72809264534753</v>
+        <v>-61.7076906289679</v>
       </c>
       <c r="J42" t="n">
-        <v>-47.17805025329558</v>
+        <v>-46.15764823691595</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>global_ind_P_fold</t>
+          <t>induction_qP_fold</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2340,34 +2309,34 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.754119254784154</v>
+        <v>0.6435676691013013</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1507233968251267</v>
+        <v>0.07444452862284283</v>
       </c>
       <c r="E43" t="n">
-        <v>0.06624535916803671</v>
+        <v>0.0134608794214452</v>
       </c>
       <c r="F43" t="n">
-        <v>0.25738173821784</v>
+        <v>0.1160210300826759</v>
       </c>
       <c r="G43" t="n">
-        <v>86.24485387074829</v>
+        <v>60.33765746917629</v>
       </c>
       <c r="H43" t="n">
-        <v>1.157215055705744</v>
+        <v>0.1223523148646213</v>
       </c>
       <c r="I43" t="n">
-        <v>-43.85974667158068</v>
+        <v>-83.69919052456692</v>
       </c>
       <c r="J43" t="n">
-        <v>-29.23323677316228</v>
+        <v>-69.07268062614851</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>induction_qP_fold</t>
+          <t>induction_rP_fold</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2376,34 +2345,34 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.8778983423636537</v>
+        <v>0.5391939524073253</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1393768234973786</v>
+        <v>0.2749525676929724</v>
       </c>
       <c r="E44" t="n">
-        <v>0.05685840978748052</v>
+        <v>0.2145810269390998</v>
       </c>
       <c r="F44" t="n">
-        <v>0.23845001528094</v>
+        <v>0.4632289141872512</v>
       </c>
       <c r="G44" t="n">
-        <v>37.87231511094296</v>
+        <v>71.60044013233511</v>
       </c>
       <c r="H44" t="n">
-        <v>0.08243138414214027</v>
+        <v>0.2944485331351723</v>
       </c>
       <c r="I44" t="n">
-        <v>-24.74224938521708</v>
+        <v>-2.164153687575606</v>
       </c>
       <c r="J44" t="n">
-        <v>-14.74368925654248</v>
+        <v>7.834406441098992</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>induction_qP_fold</t>
+          <t>induction_rP_fold</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2412,34 +2381,34 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2629263684022431</v>
+        <v>-2.23893239937099</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2819077586754642</v>
+        <v>0.6160876245804976</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2927813948281808</v>
+        <v>1.286573152245853</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5410927783921911</v>
+        <v>1.134272080343095</v>
       </c>
       <c r="G45" t="n">
-        <v>94.77844361637655</v>
+        <v>194.8509512524433</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4320690658590536</v>
+        <v>3.756561852766789</v>
       </c>
       <c r="I45" t="n">
-        <v>5.575064382489661</v>
+        <v>27.77973318848507</v>
       </c>
       <c r="J45" t="n">
-        <v>14.07166679571618</v>
+        <v>36.27633560171159</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>induction_qP_fold</t>
+          <t>induction_rP_fold</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2448,34 +2417,34 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-18.04521754098174</v>
+        <v>-943.9394266022804</v>
       </c>
       <c r="D46" t="n">
-        <v>0.267173812152838</v>
+        <v>1.882591789240281</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2500168198848894</v>
+        <v>12.40472837417507</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5000168196019904</v>
+        <v>3.52203469235825</v>
       </c>
       <c r="G46" t="n">
-        <v>497.5127061528236</v>
+        <v>3527.659456713613</v>
       </c>
       <c r="H46" t="n">
-        <v>11.78915407242789</v>
+        <v>584.3422756852134</v>
       </c>
       <c r="I46" t="n">
-        <v>-5.110768760713494</v>
+        <v>76.87963212892072</v>
       </c>
       <c r="J46" t="n">
-        <v>7.423500491967584</v>
+        <v>89.41390138160179</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>induction_qP_fold</t>
+          <t>induction_rP_fold</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2484,34 +2453,34 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.83759960128235</v>
+        <v>0.6749963201351606</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01687754774293925</v>
+        <v>0.02392058585351272</v>
       </c>
       <c r="E47" t="n">
-        <v>0.001092050302595145</v>
+        <v>0.002185464874122627</v>
       </c>
       <c r="F47" t="n">
-        <v>0.03304618438784038</v>
+        <v>0.04674895586130911</v>
       </c>
       <c r="G47" t="n">
-        <v>38.92781868835177</v>
+        <v>52.20802711860812</v>
       </c>
       <c r="H47" t="n">
-        <v>0.05548455482711161</v>
+        <v>0.1050309293713377</v>
       </c>
       <c r="I47" t="n">
-        <v>-119.2136650995288</v>
+        <v>-104.6444610366011</v>
       </c>
       <c r="J47" t="n">
-        <v>-106.6793958468477</v>
+        <v>-92.11019178392004</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>induction_qP_fold</t>
+          <t>induction_rP_fold</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2520,34 +2489,34 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.01891164643173726</v>
+        <v>0.1813493719145172</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1173893948322188</v>
+        <v>0.1150059462352605</v>
       </c>
       <c r="E48" t="n">
-        <v>0.04182090636621957</v>
+        <v>0.03489666464726583</v>
       </c>
       <c r="F48" t="n">
-        <v>0.204501604801086</v>
+        <v>0.1868064898424726</v>
       </c>
       <c r="G48" t="n">
-        <v>71.88956558000797</v>
+        <v>71.61355833176634</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3296011405268326</v>
+        <v>0.276022853678731</v>
       </c>
       <c r="I48" t="n">
-        <v>-61.7076906289679</v>
+        <v>-66.59482862604901</v>
       </c>
       <c r="J48" t="n">
-        <v>-46.15764823691595</v>
+        <v>-51.04478623399706</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>induction_qP_fold</t>
+          <t>induction_rP_fold</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2556,34 +2525,34 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.6435676691013013</v>
+        <v>0.5239840005381426</v>
       </c>
       <c r="D49" t="n">
-        <v>0.07444452862284283</v>
+        <v>0.09058039817603264</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0134608794214452</v>
+        <v>0.01797702794041958</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1160210300826759</v>
+        <v>0.1340784395062069</v>
       </c>
       <c r="G49" t="n">
-        <v>60.33765746917629</v>
+        <v>69.62930601396636</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1223523148646213</v>
+        <v>0.161388719396851</v>
       </c>
       <c r="I49" t="n">
-        <v>-83.69919052456692</v>
+        <v>-76.46651404218929</v>
       </c>
       <c r="J49" t="n">
-        <v>-69.07268062614851</v>
+        <v>-61.84000414377088</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>induction_rP_fold</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2592,34 +2561,34 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9186743790788644</v>
+        <v>0.3727225967834948</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1132248170747432</v>
+        <v>0.2622257011901458</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03787045622531155</v>
+        <v>0.2921008308399405</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1946033304579126</v>
+        <v>0.5404635333118605</v>
       </c>
       <c r="G50" t="n">
-        <v>29.44985263816072</v>
+        <v>42.01778878792659</v>
       </c>
       <c r="H50" t="n">
-        <v>0.05690700563405877</v>
+        <v>0.3986538025529099</v>
       </c>
       <c r="I50" t="n">
-        <v>-31.65092782996324</v>
+        <v>3.078844171186496</v>
       </c>
       <c r="J50" t="n">
-        <v>-21.65236770128865</v>
+        <v>13.07740429986109</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>induction_rP_fold</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2628,34 +2597,34 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.955277502122106</v>
+        <v>0.601776087518032</v>
       </c>
       <c r="D51" t="n">
-        <v>0.07937287997870515</v>
+        <v>0.1557010632353629</v>
       </c>
       <c r="E51" t="n">
-        <v>0.01776473170055809</v>
+        <v>0.1581830465128266</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1332844015650672</v>
+        <v>0.3977223233775375</v>
       </c>
       <c r="G51" t="n">
-        <v>37.93689786404471</v>
+        <v>31.64442937755998</v>
       </c>
       <c r="H51" t="n">
-        <v>0.03185206155375885</v>
+        <v>0.236195306303569</v>
       </c>
       <c r="I51" t="n">
-        <v>-36.45810228482799</v>
+        <v>-3.660035914366656</v>
       </c>
       <c r="J51" t="n">
-        <v>-27.96149987160147</v>
+        <v>4.836566498859863</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>induction_rP_fold</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2664,34 +2633,34 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.7750807780357274</v>
+        <v>-2.292501058686348</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0283251512038041</v>
+        <v>0.0971029138896892</v>
       </c>
       <c r="E52" t="n">
-        <v>0.00295263566748381</v>
+        <v>0.04322243326383968</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0543381603248013</v>
+        <v>0.2079000559495829</v>
       </c>
       <c r="G52" t="n">
-        <v>53.48070562757869</v>
+        <v>143.0485653997427</v>
       </c>
       <c r="H52" t="n">
-        <v>0.07554261155652046</v>
+        <v>2.048012041781185</v>
       </c>
       <c r="I52" t="n">
-        <v>-98.32619827914304</v>
+        <v>-41.96930823001863</v>
       </c>
       <c r="J52" t="n">
-        <v>-85.79192902646196</v>
+        <v>-29.43503897733755</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>induction_rP_fold</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2700,34 +2669,34 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.4468046350834405</v>
+        <v>-10.4235652104228</v>
       </c>
       <c r="D53" t="n">
-        <v>0.03122422893728921</v>
+        <v>0.1264924492953734</v>
       </c>
       <c r="E53" t="n">
-        <v>0.003719924153029212</v>
+        <v>0.07681697793394504</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06099118094470062</v>
+        <v>0.2771587594393239</v>
       </c>
       <c r="G53" t="n">
-        <v>70.7755309332148</v>
+        <v>241.0218086385581</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1745625563820883</v>
+        <v>6.973682895361207</v>
       </c>
       <c r="I53" t="n">
-        <v>-93.47509199738721</v>
+        <v>-29.8929215246508</v>
       </c>
       <c r="J53" t="n">
-        <v>-80.94082274470614</v>
+        <v>-17.35865227196972</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>induction_rP_fold</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2736,34 +2705,34 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.7908835757779235</v>
+        <v>0.6319812958585576</v>
       </c>
       <c r="D54" t="n">
-        <v>0.05618966172770314</v>
+        <v>0.06340137598747402</v>
       </c>
       <c r="E54" t="n">
-        <v>0.008914017137419438</v>
+        <v>0.01568755322692337</v>
       </c>
       <c r="F54" t="n">
-        <v>0.09441407277212141</v>
+        <v>0.1252499629817245</v>
       </c>
       <c r="G54" t="n">
-        <v>37.58690526144422</v>
+        <v>40.12670930054983</v>
       </c>
       <c r="H54" t="n">
-        <v>0.07497473926281659</v>
+        <v>0.1273868985012791</v>
       </c>
       <c r="I54" t="n">
-        <v>-103.4435176121391</v>
+        <v>-88.18196706690422</v>
       </c>
       <c r="J54" t="n">
-        <v>-87.89347522008715</v>
+        <v>-72.63192467485227</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>induction_rP_fold</t>
+          <t>induction_P_fold</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2772,244 +2741,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-3.637774300383827</v>
+        <v>0.447258575977301</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2546568715998175</v>
+        <v>0.09935275018770522</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1751483107156371</v>
+        <v>0.02087460932976388</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4185072409357299</v>
+        <v>0.1444804807915723</v>
       </c>
       <c r="G55" t="n">
-        <v>135.7491627177002</v>
+        <v>75.89669421584698</v>
       </c>
       <c r="H55" t="n">
-        <v>3.039872215232188</v>
+        <v>0.1864346537376445</v>
       </c>
       <c r="I55" t="n">
-        <v>-19.55305435429238</v>
+        <v>-72.73054307905477</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.926544455873973</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>BR02</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0.07857686751760085</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.3333337353130066</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.4290740606518431</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.6550374498086678</v>
-      </c>
-      <c r="G56" t="n">
-        <v>55.21890071551628</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.5827787822010099</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.615862430168713</v>
-      </c>
-      <c r="J56" t="n">
-        <v>19.61442255884331</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>BR03</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0.462120720638594</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.1677181877507518</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.2136571421219302</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.4622306157341054</v>
-      </c>
-      <c r="G57" t="n">
-        <v>29.14891464495499</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.316923783293773</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.8492596743663299</v>
-      </c>
-      <c r="J57" t="n">
-        <v>9.345862087592849</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>BR04</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.8963766886448536</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.01849844643236161</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.001360318973264927</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.0368825022641486</v>
-      </c>
-      <c r="G58" t="n">
-        <v>34.90224278706977</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.03803921668782936</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-114.6007574189448</v>
-      </c>
-      <c r="J58" t="n">
-        <v>-102.0664881662637</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>BR05</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>0.6900480364085393</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.02354891371535377</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.002084250644104035</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.04565359398890776</v>
-      </c>
-      <c r="G59" t="n">
-        <v>55.93598465298017</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.1004445645283111</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-105.6402637244324</v>
-      </c>
-      <c r="J59" t="n">
-        <v>-93.1059944717513</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>BR07</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>0.1707396630055101</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.08416859522791051</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.03534892528336719</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.1880130987015724</v>
-      </c>
-      <c r="G60" t="n">
-        <v>48.67700964922973</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.279522348796704</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-66.2471568102776</v>
-      </c>
-      <c r="J60" t="n">
-        <v>-50.69711441822565</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>induction_P_fold</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.08254506559110553</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0.1257882467589217</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.04088295963349029</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.2021953501777187</v>
-      </c>
-      <c r="G61" t="n">
-        <v>84.64490028401899</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.7187631828415498</v>
-      </c>
-      <c r="I61" t="n">
-        <v>-55.92604844069487</v>
-      </c>
-      <c r="J61" t="n">
-        <v>-41.29953854227647</v>
+        <v>-58.10403318063636</v>
       </c>
     </row>
   </sheetData>
